--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>10.55</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>17.62</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -433,7 +433,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>55.76</v>
+        <v>52.68</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -441,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>81.67</v>
+        <v>78.76000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -449,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>88.12</v>
+        <v>92.42</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>4.85</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -465,7 +465,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>23.9</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -473,7 +473,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>56.96</v>
+        <v>53.32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>7.16</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>12.4</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -449,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>92.42</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>6.92</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>11.95</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -433,7 +433,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>52.68</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -441,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>78.76000000000001</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -449,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>92.70999999999999</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>2.73</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -465,7 +465,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>27.8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -473,7 +473,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>53.32</v>
+        <v>28.04</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>7.63</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>7.64</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>12.63</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -433,7 +433,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>35.06</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -441,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>56.33</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -449,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>89.75</v>
+        <v>90.98</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5.22</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -465,7 +465,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>57</v>
+        <v>58.74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -473,7 +473,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>28.04</v>
+        <v>25.92</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>6.6</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>11.15</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -433,7 +433,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>34.46</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -441,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>55.85</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -449,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>90.98</v>
+        <v>90.37</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>4.64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -465,7 +465,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>58.74</v>
+        <v>59.97</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -473,7 +473,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>25.92</v>
+        <v>25.14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>7.02</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>11.79</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -449,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>90.37</v>
+        <v>90.75</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>6.77</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>11.35</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -433,7 +433,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>33.51</v>
+        <v>31.93</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -441,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>54.54</v>
+        <v>52.16</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -449,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>90.75</v>
+        <v>91.92</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>4.79</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -465,7 +465,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>59.97</v>
+        <v>61.33</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -473,7 +473,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>25.14</v>
+        <v>24.56</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -433,7 +433,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>31.93</v>
+        <v>31.41</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -441,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>52.16</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -465,7 +465,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>61.33</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -473,7 +473,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>24.56</v>
+        <v>24.01</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>6.08</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>10.15</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -433,7 +433,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>31.41</v>
+        <v>38.35</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -441,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>51.36</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -449,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>91.92</v>
+        <v>93.08</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>4.12</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -465,7 +465,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>62.05</v>
+        <v>49.79</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -473,7 +473,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>24.01</v>
+        <v>34.63</v>
       </c>
     </row>
   </sheetData>
